--- a/ig/ch-core/StructureDefinition-ch-core-medicationdispense.xlsx
+++ b/ig/ch-core/StructureDefinition-ch-core-medicationdispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="383">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T08:02:49+00:00</t>
+    <t>2026-06-10T15:05:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -469,6 +469,16 @@
   </si>
   <si>
     <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>MedicationDispense.extension:indicationCode</t>
+  </si>
+  <si>
+    <t>indicationCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://fhir.ch/ig/ch-core/StructureDefinition/ch-ext-epl-regulated-authorization-limitation-indication-code}
 </t>
   </si>
   <si>
@@ -1512,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO47"/>
+  <dimension ref="A1:AO48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.2578125" customWidth="true" bestFit="true"/>
@@ -2732,43 +2742,41 @@
         <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>80</v>
       </c>
@@ -2816,7 +2824,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -2825,7 +2833,7 @@
         <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>140</v>
@@ -2848,14 +2856,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2868,24 +2876,26 @@
         <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>80</v>
       </c>
@@ -2933,7 +2943,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -2945,19 +2955,19 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>80</v>
@@ -2965,10 +2975,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2991,15 +3001,17 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -3048,7 +3060,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3063,16 +3075,16 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>80</v>
@@ -3080,10 +3092,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3091,32 +3103,30 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>80</v>
@@ -3141,13 +3151,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3165,13 +3175,13 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>80</v>
@@ -3180,16 +3190,16 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>80</v>
@@ -3197,10 +3207,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3208,7 +3218,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>89</v>
@@ -3217,21 +3227,23 @@
         <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>181</v>
+        <v>109</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3256,13 +3268,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3280,10 +3292,10 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>89</v>
@@ -3295,16 +3307,16 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
@@ -3312,10 +3324,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3338,17 +3350,15 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3373,13 +3383,13 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3397,7 +3407,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3412,10 +3422,10 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>80</v>
@@ -3429,10 +3439,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3440,7 +3450,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>89</v>
@@ -3452,19 +3462,19 @@
         <v>80</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3490,13 +3500,13 @@
         <v>80</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>184</v>
+        <v>113</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>80</v>
@@ -3514,10 +3524,10 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>89</v>
@@ -3529,27 +3539,27 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>206</v>
+        <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3557,7 +3567,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
@@ -3572,16 +3582,16 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3607,13 +3617,13 @@
         <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>80</v>
@@ -3631,10 +3641,10 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>89</v>
@@ -3646,27 +3656,27 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3686,18 +3696,20 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -3746,7 +3758,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -3761,27 +3773,27 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>80</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3792,7 +3804,7 @@
         <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>80</v>
@@ -3804,13 +3816,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3861,13 +3873,13 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
@@ -3876,13 +3888,13 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>80</v>
+        <v>225</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>229</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>80</v>
@@ -3893,10 +3905,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3919,13 +3931,13 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3976,7 +3988,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -3991,13 +4003,13 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>234</v>
+        <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>80</v>
+        <v>232</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>80</v>
@@ -4008,10 +4020,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4022,7 +4034,7 @@
         <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>80</v>
@@ -4034,13 +4046,13 @@
         <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4091,25 +4103,25 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>80</v>
+        <v>237</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
@@ -4123,21 +4135,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>80</v>
@@ -4149,17 +4161,15 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>134</v>
+        <v>240</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4208,25 +4218,25 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>80</v>
@@ -4240,14 +4250,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>247</v>
+        <v>151</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4260,26 +4270,24 @@
         <v>80</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>80</v>
       </c>
@@ -4327,7 +4335,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4345,7 +4353,7 @@
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>132</v>
+        <v>244</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>80</v>
@@ -4359,43 +4367,45 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M25" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N25" s="2"/>
+      <c r="N25" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O25" t="s" s="2">
-        <v>254</v>
+        <v>155</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4420,13 +4430,13 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>255</v>
+        <v>80</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>256</v>
+        <v>80</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
@@ -4444,25 +4454,25 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>257</v>
+        <v>132</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>80</v>
@@ -4476,10 +4486,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4487,7 +4497,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>89</v>
@@ -4502,16 +4512,18 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>259</v>
+        <v>193</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
       </c>
@@ -4535,13 +4547,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>80</v>
+        <v>259</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -4559,10 +4571,10 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>89</v>
@@ -4574,10 +4586,10 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
@@ -4591,10 +4603,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4602,7 +4614,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>89</v>
@@ -4617,13 +4629,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4674,10 +4686,10 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>89</v>
@@ -4689,10 +4701,10 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
@@ -4706,10 +4718,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4720,7 +4732,7 @@
         <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -4732,17 +4744,15 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>273</v>
-      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -4791,13 +4801,13 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
@@ -4806,27 +4816,27 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>276</v>
+        <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>277</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4837,7 +4847,7 @@
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>80</v>
@@ -4849,15 +4859,17 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>190</v>
+        <v>273</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -4882,13 +4894,13 @@
         <v>80</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>80</v>
@@ -4906,13 +4918,13 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
@@ -4921,27 +4933,27 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>80</v>
+        <v>277</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4964,13 +4976,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>286</v>
+        <v>193</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4997,13 +5009,13 @@
         <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>80</v>
+        <v>283</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>80</v>
@@ -5021,7 +5033,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5039,24 +5051,24 @@
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5079,13 +5091,13 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5136,7 +5148,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5154,24 +5166,24 @@
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5191,16 +5203,16 @@
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5251,7 +5263,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5269,24 +5281,24 @@
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>302</v>
+        <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5306,16 +5318,16 @@
         <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5366,7 +5378,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5381,27 +5393,27 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>307</v>
+        <v>80</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5424,13 +5436,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5481,7 +5493,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5496,27 +5508,27 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>80</v>
+        <v>310</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5527,7 +5539,7 @@
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>80</v>
@@ -5539,13 +5551,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>316</v>
+        <v>268</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5596,13 +5608,13 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
@@ -5614,24 +5626,24 @@
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>80</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5654,13 +5666,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5711,7 +5723,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5726,27 +5738,27 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>325</v>
+        <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>327</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5769,17 +5781,15 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -5828,7 +5838,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -5843,10 +5853,10 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>80</v>
+        <v>328</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>80</v>
@@ -5855,15 +5865,15 @@
         <v>80</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>80</v>
+        <v>330</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5874,7 +5884,7 @@
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
@@ -5886,15 +5896,17 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>231</v>
+        <v>332</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M38" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -5943,31 +5955,31 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>337</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>339</v>
+        <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -5975,10 +5987,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6001,13 +6013,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>238</v>
+        <v>338</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>239</v>
+        <v>339</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6058,7 +6070,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>240</v>
+        <v>337</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6070,19 +6082,19 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>80</v>
+        <v>340</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>241</v>
+        <v>341</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
@@ -6090,21 +6102,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>80</v>
@@ -6116,17 +6128,15 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>134</v>
+        <v>240</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6175,25 +6185,25 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
@@ -6207,14 +6217,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>247</v>
+        <v>151</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6227,26 +6237,24 @@
         <v>80</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>80</v>
       </c>
@@ -6294,7 +6302,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6312,7 +6320,7 @@
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>132</v>
+        <v>244</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
@@ -6326,42 +6334,46 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>344</v>
+        <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>345</v>
+        <v>251</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
@@ -6409,25 +6421,25 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>343</v>
+        <v>253</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>347</v>
+        <v>132</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
@@ -6441,10 +6453,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6452,7 +6464,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -6467,13 +6479,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>190</v>
+        <v>347</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6500,11 +6512,13 @@
         <v>80</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>351</v>
+        <v>80</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>80</v>
@@ -6522,10 +6536,10 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>89</v>
@@ -6540,24 +6554,24 @@
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>282</v>
+        <v>350</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>353</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6568,7 +6582,7 @@
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>80</v>
@@ -6580,13 +6594,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6613,13 +6627,11 @@
         <v>80</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>80</v>
@@ -6637,13 +6649,13 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
@@ -6655,24 +6667,24 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>359</v>
+        <v>285</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>80</v>
+        <v>356</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6695,13 +6707,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>362</v>
+        <v>193</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6728,13 +6740,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>80</v>
+        <v>360</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>80</v>
+        <v>361</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -6752,7 +6764,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -6770,13 +6782,13 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
@@ -6784,14 +6796,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>368</v>
+        <v>80</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6810,17 +6822,15 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -6869,7 +6879,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -6887,13 +6897,13 @@
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>80</v>
+        <v>369</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -6901,14 +6911,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>80</v>
+        <v>371</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6927,16 +6937,16 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6986,7 +6996,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7004,15 +7014,132 @@
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO47" t="s" s="2">
+      <c r="M48" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>80</v>
       </c>
     </row>
